--- a/Planification.xlsx
+++ b/Planification.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jamil.gammoudi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jamil.gammoudi\Documents\GitHub\mon-horaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C26AB7BB-10AC-4F07-9BE3-203C18AE0FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E927EBA-D642-4316-A865-D07B73BED72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{EFF68EF8-472A-447C-A619-AFB977E34341}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{EFF68EF8-472A-447C-A619-AFB977E34341}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="139">
   <si>
     <t>Proposition 1</t>
   </si>
@@ -204,16 +204,7 @@
     <t>Semaine 3</t>
   </si>
   <si>
-    <t>18h15 à 22h15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Portes ouvertes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Techniques d'apprentissage </t>
-  </si>
-  <si>
-    <t>Geneviève Labelle</t>
   </si>
   <si>
     <t>9 nov. 2026</t>
@@ -1016,15 +1007,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1200,6 +1182,100 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1209,102 +1285,17 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1321,10 +1312,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1656,33 +1643,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
     </row>
     <row r="2" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
     </row>
     <row r="4" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E4" s="14" t="s">
@@ -3081,14 +3068,14 @@
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="113"/>
+      <c r="I43" s="113"/>
+      <c r="J43" s="113"/>
     </row>
     <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -4414,1806 +4401,1865 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="C7" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-    </row>
-    <row r="8" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="90"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="91" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="35" t="s">
+      <c r="A15" s="31"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="35" t="s">
+      <c r="D15" s="25"/>
+      <c r="E15" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="28"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="37" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="28"/>
+      <c r="E16" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="37" t="s">
+      <c r="A17" s="35"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="37" t="s">
+      <c r="D17" s="43"/>
+      <c r="E17" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="37" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="37" t="s">
+      <c r="D18" s="28"/>
+      <c r="E18" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="89" t="s">
+      <c r="E19" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="89" t="s">
+      <c r="F19" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
-      <c r="B21" s="35" t="s">
+      <c r="A21" s="36"/>
+      <c r="B21" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="37" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
-      <c r="B23" s="37" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="37" t="s">
+      <c r="A24" s="33"/>
+      <c r="B24" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="91" t="s">
         <v>50</v>
       </c>
       <c r="E25" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="89" t="s">
+      <c r="F25" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="27" t="s">
+      <c r="A27" s="36"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="97" t="s">
+      <c r="E27" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="25"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="33"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="28"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="35"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="43"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="33"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F27" s="28"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="30" t="s">
+      <c r="B31" s="91" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="98"/>
-      <c r="E28" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="30" t="s">
+      <c r="D31" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="98"/>
-      <c r="E29" s="114" t="s">
+      <c r="E31" s="96"/>
+      <c r="F31" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="36"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="25"/>
+      <c r="E33" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F33" s="25"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="33"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="28"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="35"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="30" t="s">
+      <c r="D35" s="43"/>
+      <c r="E35" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="43"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="33"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="89" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="89" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="89" t="s">
+      <c r="D36" s="28"/>
+      <c r="E36" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F36" s="28"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E31" s="96"/>
-      <c r="F31" s="89" t="s">
+      <c r="B37" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33" t="s">
+      <c r="D37" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="35" t="s">
+      <c r="E37" s="96" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="92"/>
+      <c r="C38" s="92"/>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="36"/>
+      <c r="B39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F33" s="28"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="37" t="s">
+      <c r="C39" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="25"/>
+      <c r="E39" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F39" s="25"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="33"/>
+      <c r="B40" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="31"/>
-      <c r="E34" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="37" t="s">
+      <c r="C40" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="28"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="35"/>
+      <c r="B41" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="46"/>
-      <c r="E35" s="114" t="s">
+      <c r="C41" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="46"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-    </row>
-    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="37" t="s">
+      <c r="D41" s="43"/>
+      <c r="E41" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="33"/>
+      <c r="B42" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="89" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" s="89" t="s">
-        <v>65</v>
-      </c>
-      <c r="E37" s="96" t="s">
+      <c r="C42" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="28"/>
+      <c r="E42" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="89" t="s">
+      <c r="B43" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="33" t="s">
+      <c r="D43" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="90"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="90"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-    </row>
-    <row r="39" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
-      <c r="B39" s="35" t="s">
+      <c r="E43" s="96" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="92"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="92"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="D45" s="25"/>
+      <c r="E45" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F45" s="25"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="33"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="28"/>
+      <c r="E46" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="28"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="35"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="43"/>
+      <c r="E47" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="43"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="33"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="28"/>
+      <c r="E48" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F48" s="28"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+    </row>
+    <row r="49" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="91" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" s="96" t="s">
+        <v>75</v>
+      </c>
+      <c r="F49" s="91" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="92"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="92"/>
+      <c r="E50" s="92"/>
+      <c r="F50" s="92"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+    </row>
+    <row r="51" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="36"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="37" t="s">
+      <c r="D51" s="25"/>
+      <c r="E51" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F51" s="25"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="33"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="D52" s="28"/>
+      <c r="E52" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F52" s="28"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="35"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="43"/>
+      <c r="E53" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" s="43"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="33"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="28"/>
+      <c r="E54" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F54" s="28"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="91" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B56" s="92"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="16"/>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="40"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="25"/>
+      <c r="E57" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" s="25"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="41"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="31"/>
-      <c r="E40" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="38"/>
-      <c r="B41" s="37" t="s">
+      <c r="D58" s="28"/>
+      <c r="E58" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" s="28"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="42"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="37" t="s">
+      <c r="D59" s="43"/>
+      <c r="E59" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="46"/>
-      <c r="E41" s="114" t="s">
+      <c r="F59" s="43"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+    </row>
+    <row r="60" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="41"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" s="28"/>
+      <c r="E60" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="28"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" s="91" t="s">
+        <v>86</v>
+      </c>
+      <c r="E61" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" s="92"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="40"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="25"/>
+      <c r="E63" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F63" s="25"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="41"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="28"/>
+      <c r="E64" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F64" s="28"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="42"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F41" s="46"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-      <c r="B42" s="37" t="s">
+      <c r="D65" s="43"/>
+      <c r="E65" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F65" s="43"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16"/>
+    </row>
+    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="41"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="37" t="s">
+      <c r="D66" s="28"/>
+      <c r="E66" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F66" s="28"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+    </row>
+    <row r="67" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" s="91" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" s="96" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+    </row>
+    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="30"/>
+      <c r="B68" s="92"/>
+      <c r="C68" s="92"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="92"/>
+      <c r="F68" s="92"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+    </row>
+    <row r="69" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="40"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="41"/>
+      <c r="B70" s="46"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="42"/>
+      <c r="B71" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C71" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="F71" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+    </row>
+    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="41"/>
+      <c r="B72" s="46"/>
+      <c r="C72" s="47"/>
+      <c r="D72" s="47"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="47"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="91" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="30"/>
+      <c r="B74" s="92"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="92"/>
+      <c r="E74" s="92"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="40"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="41"/>
+      <c r="B76" s="47"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="47"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="42"/>
+      <c r="B77" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E77" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="F77" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="49"/>
+      <c r="B78" s="47"/>
+      <c r="C78" s="47"/>
+      <c r="D78" s="47"/>
+      <c r="E78" s="47"/>
+      <c r="F78" s="47"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+    </row>
+    <row r="79" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B79" s="91" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="E79" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="F79" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" s="92"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="92"/>
+      <c r="F80" s="92"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+    </row>
+    <row r="81" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="50"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" s="25"/>
+      <c r="E81" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F81" s="25"/>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="16"/>
+      <c r="J81" s="16"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="51"/>
+      <c r="B82" s="47"/>
+      <c r="C82" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="28"/>
+      <c r="E82" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F82" s="28"/>
+      <c r="G82" s="52"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+      <c r="J82" s="16"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="53"/>
+      <c r="B83" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="43"/>
+      <c r="E83" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83" s="43"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="16"/>
+    </row>
+    <row r="84" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="51"/>
+      <c r="B84" s="47"/>
+      <c r="C84" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="31"/>
-      <c r="E42" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43" s="89" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="89" t="s">
-        <v>70</v>
-      </c>
-      <c r="D43" s="89" t="s">
-        <v>71</v>
-      </c>
-      <c r="E43" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" s="90"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="90"/>
-      <c r="F44" s="90"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="39"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="35" t="s">
+      <c r="D84" s="28"/>
+      <c r="E84" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F84" s="28"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
+      <c r="J84" s="16"/>
+    </row>
+    <row r="85" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
+      <c r="I85" s="16"/>
+      <c r="J85" s="16"/>
+    </row>
+    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" s="54"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
+      <c r="I86" s="16"/>
+      <c r="J86" s="16"/>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="93"/>
+      <c r="B87" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D45" s="28"/>
-      <c r="E45" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F45" s="28"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="37" t="s">
+      <c r="C87" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="25"/>
+      <c r="E87" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F87" s="25"/>
+      <c r="G87" s="86"/>
+      <c r="H87" s="86"/>
+      <c r="I87" s="86"/>
+      <c r="J87" s="86"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="94"/>
+      <c r="B88" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="31"/>
-      <c r="E46" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="38"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="37" t="s">
+      <c r="C88" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="28"/>
+      <c r="E88" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F88" s="28"/>
+      <c r="G88" s="86"/>
+      <c r="H88" s="86"/>
+      <c r="I88" s="86"/>
+      <c r="J88" s="86"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="94"/>
+      <c r="B89" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="46"/>
-      <c r="E47" s="114" t="s">
+      <c r="C89" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F47" s="46"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-    </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="37" t="s">
+      <c r="D89" s="43"/>
+      <c r="E89" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" s="43"/>
+      <c r="G89" s="86"/>
+      <c r="H89" s="86"/>
+      <c r="I89" s="86"/>
+      <c r="J89" s="86"/>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="95"/>
+      <c r="B90" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="31"/>
-      <c r="E48" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F48" s="31"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-    </row>
-    <row r="49" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" s="89" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="89" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="89" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" s="96" t="s">
-        <v>78</v>
-      </c>
-      <c r="F49" s="89" t="s">
-        <v>79</v>
-      </c>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-    </row>
-    <row r="50" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" s="90"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="90"/>
-      <c r="F50" s="90"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-    </row>
-    <row r="51" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="35" t="s">
+      <c r="C90" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="28"/>
+      <c r="E90" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F90" s="28"/>
+      <c r="G90" s="86"/>
+      <c r="H90" s="86"/>
+      <c r="I90" s="86"/>
+      <c r="J90" s="86"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F91" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B92" s="54"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="50"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="28"/>
-      <c r="E51" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F51" s="28"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
-      <c r="B52" s="41"/>
-      <c r="C52" s="37" t="s">
+      <c r="D93" s="25"/>
+      <c r="E93" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="F93" s="25"/>
+      <c r="G93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="51"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="31"/>
-      <c r="E52" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="38"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="37" t="s">
+      <c r="D94" s="28"/>
+      <c r="E94" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F94" s="28"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="53"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="46"/>
-      <c r="E53" s="114" t="s">
+      <c r="D95" s="43"/>
+      <c r="E95" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="46"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-    </row>
-    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="36"/>
-      <c r="B54" s="41"/>
-      <c r="C54" s="37" t="s">
+      <c r="F95" s="43"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+    </row>
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="51"/>
+      <c r="B96" s="55"/>
+      <c r="C96" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="D54" s="31"/>
-      <c r="E54" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="31"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="89" t="s">
-        <v>82</v>
-      </c>
-      <c r="D55" s="89" t="s">
-        <v>83</v>
-      </c>
-      <c r="E55" s="96" t="s">
-        <v>84</v>
-      </c>
-      <c r="F55" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="B56" s="90"/>
-      <c r="C56" s="90"/>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="19"/>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="43"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D57" s="28"/>
-      <c r="E57" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F57" s="28"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="44"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="37" t="s">
+      <c r="D96" s="28"/>
+      <c r="E96" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F96" s="28"/>
+      <c r="G96" s="16"/>
+      <c r="H96" s="16"/>
+      <c r="I96" s="16"/>
+      <c r="J96" s="16"/>
+    </row>
+    <row r="97" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="16"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="57"/>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="16"/>
+      <c r="H98" s="16"/>
+      <c r="I98" s="16"/>
+      <c r="J98" s="16"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="57"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="16"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+      <c r="J99" s="16"/>
+    </row>
+    <row r="100" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B100" s="87" t="s">
+        <v>120</v>
+      </c>
+      <c r="C100" s="88"/>
+      <c r="D100" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="E100" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="F100" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+      <c r="J100" s="16"/>
+    </row>
+    <row r="101" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B101" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="C101" s="90"/>
+      <c r="D101" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="F101" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="16"/>
+      <c r="J101" s="16"/>
+    </row>
+    <row r="102" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="31"/>
-      <c r="E58" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F58" s="31"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="45"/>
-      <c r="B59" s="41"/>
-      <c r="C59" s="37" t="s">
+      <c r="B102" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="C102" s="81"/>
+      <c r="D102" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="E102" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="46"/>
-      <c r="E59" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="F59" s="46"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
-    </row>
-    <row r="60" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="44"/>
-      <c r="B60" s="41"/>
-      <c r="C60" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="31"/>
-      <c r="E60" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F60" s="31"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-    </row>
-    <row r="61" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" s="89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C61" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="96" t="s">
-        <v>90</v>
-      </c>
-      <c r="F61" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-    </row>
-    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B62" s="90"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-    </row>
-    <row r="63" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="43"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" s="28"/>
-      <c r="E63" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F63" s="28"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="44"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="D64" s="31"/>
-      <c r="E64" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F64" s="31"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="45"/>
-      <c r="B65" s="46"/>
-      <c r="C65" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" s="46"/>
-      <c r="E65" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="F65" s="46"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-    </row>
-    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="44"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66" s="31"/>
-      <c r="E66" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F66" s="31"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-    </row>
-    <row r="67" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B67" s="89" t="s">
-        <v>93</v>
-      </c>
-      <c r="C67" s="89" t="s">
-        <v>94</v>
-      </c>
-      <c r="D67" s="89" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="F67" s="89" t="s">
-        <v>97</v>
-      </c>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
-    </row>
-    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="90"/>
-      <c r="C68" s="90"/>
-      <c r="D68" s="90"/>
-      <c r="E68" s="90"/>
-      <c r="F68" s="90"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
-    </row>
-    <row r="69" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="43"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="44"/>
-      <c r="B70" s="49"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="45"/>
-      <c r="B71" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D71" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="E71" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="F71" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
-    </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="44"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
-    </row>
-    <row r="73" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B73" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="C73" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73" s="89" t="s">
-        <v>101</v>
-      </c>
-      <c r="E73" s="89" t="s">
-        <v>102</v>
-      </c>
-      <c r="F73" s="89" t="s">
-        <v>103</v>
-      </c>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="33"/>
-      <c r="B74" s="90"/>
-      <c r="C74" s="90"/>
-      <c r="D74" s="90"/>
-      <c r="E74" s="90"/>
-      <c r="F74" s="90"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="43"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="44"/>
-      <c r="B76" s="50"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="45"/>
-      <c r="B77" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C77" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D77" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="E77" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="F77" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="52"/>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50"/>
-      <c r="D78" s="50"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-    </row>
-    <row r="79" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B79" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="C79" s="89" t="s">
-        <v>105</v>
-      </c>
-      <c r="D79" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="E79" s="89" t="s">
-        <v>107</v>
-      </c>
-      <c r="F79" s="89" t="s">
-        <v>108</v>
-      </c>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="B80" s="90"/>
-      <c r="C80" s="90"/>
-      <c r="D80" s="90"/>
-      <c r="E80" s="90"/>
-      <c r="F80" s="90"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
-    </row>
-    <row r="81" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="53"/>
-      <c r="B81" s="48"/>
-      <c r="C81" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D81" s="28"/>
-      <c r="E81" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F81" s="28"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="19"/>
-      <c r="I81" s="19"/>
-      <c r="J81" s="19"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="54"/>
-      <c r="B82" s="50"/>
-      <c r="C82" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="D82" s="31"/>
-      <c r="E82" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F82" s="31"/>
-      <c r="G82" s="55"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="56"/>
-      <c r="B83" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C83" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D83" s="46"/>
-      <c r="E83" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="F83" s="46"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
-    </row>
-    <row r="84" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="54"/>
-      <c r="B84" s="50"/>
-      <c r="C84" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D84" s="31"/>
-      <c r="E84" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F84" s="31"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
-    </row>
-    <row r="85" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B85" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="C85" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E85" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="F85" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="19"/>
-    </row>
-    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B86" s="57"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="100"/>
-      <c r="B87" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D87" s="28"/>
-      <c r="E87" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F87" s="28"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="84"/>
-      <c r="I87" s="84"/>
-      <c r="J87" s="84"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="101"/>
-      <c r="B88" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="D88" s="31"/>
-      <c r="E88" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F88" s="31"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
-      <c r="I88" s="84"/>
-      <c r="J88" s="84"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="101"/>
-      <c r="B89" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="C89" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D89" s="46"/>
-      <c r="E89" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="F89" s="46"/>
-      <c r="G89" s="84"/>
-      <c r="H89" s="84"/>
-      <c r="I89" s="84"/>
-      <c r="J89" s="84"/>
-    </row>
-    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="102"/>
-      <c r="B90" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="C90" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D90" s="31"/>
-      <c r="E90" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F90" s="31"/>
-      <c r="G90" s="84"/>
-      <c r="H90" s="84"/>
-      <c r="I90" s="84"/>
-      <c r="J90" s="84"/>
-    </row>
-    <row r="91" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B91" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="C91" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E91" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F91" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="G91" s="19"/>
-      <c r="H91" s="19"/>
-      <c r="I91" s="19"/>
-      <c r="J91" s="19"/>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="B92" s="57"/>
-      <c r="C92" s="57"/>
-      <c r="D92" s="57"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="19"/>
-      <c r="H92" s="19"/>
-      <c r="I92" s="19"/>
-      <c r="J92" s="19"/>
-    </row>
-    <row r="93" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="53"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D93" s="28"/>
-      <c r="E93" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="F93" s="28"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="19"/>
-      <c r="I93" s="19"/>
-      <c r="J93" s="19"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="54"/>
-      <c r="B94" s="41"/>
-      <c r="C94" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="D94" s="31"/>
-      <c r="E94" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="F94" s="31"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="19"/>
-      <c r="I94" s="19"/>
-      <c r="J94" s="19"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="56"/>
-      <c r="B95" s="41"/>
-      <c r="C95" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D95" s="46"/>
-      <c r="E95" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="F95" s="46"/>
-      <c r="G95" s="19"/>
-      <c r="H95" s="19"/>
-      <c r="I95" s="19"/>
-      <c r="J95" s="19"/>
-    </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="54"/>
-      <c r="B96" s="58"/>
-      <c r="C96" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="D96" s="31"/>
-      <c r="E96" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="F96" s="31"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="19"/>
-      <c r="I96" s="19"/>
-      <c r="J96" s="19"/>
-    </row>
-    <row r="97" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="19"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="60"/>
-      <c r="B98" s="60"/>
-      <c r="C98" s="60"/>
-      <c r="D98" s="60"/>
-      <c r="E98" s="60"/>
-      <c r="F98" s="60"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="19"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="60"/>
-      <c r="B99" s="60"/>
-      <c r="C99" s="60"/>
-      <c r="D99" s="60"/>
-      <c r="E99" s="60"/>
-      <c r="F99" s="60"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="19"/>
-      <c r="I99" s="19"/>
-      <c r="J99" s="19"/>
-    </row>
-    <row r="100" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="61" t="s">
-        <v>122</v>
-      </c>
-      <c r="B100" s="103" t="s">
-        <v>123</v>
-      </c>
-      <c r="C100" s="104"/>
-      <c r="D100" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="E100" s="62" t="s">
+      <c r="F102" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="16"/>
+      <c r="J102" s="16"/>
+    </row>
+    <row r="103" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="B103" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103" s="83"/>
+      <c r="D103" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="F100" s="63" t="s">
-        <v>126</v>
-      </c>
-      <c r="G100" s="19"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="19"/>
-      <c r="J100" s="19"/>
-    </row>
-    <row r="101" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="B101" s="105" t="s">
-        <v>127</v>
-      </c>
-      <c r="C101" s="106"/>
-      <c r="D101" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="E101" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="F101" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="G101" s="19"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="19"/>
-      <c r="J101" s="19"/>
-    </row>
-    <row r="102" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="68" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="C102" s="108"/>
-      <c r="D102" s="69" t="s">
+      <c r="E103" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="E102" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="71" t="s">
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="16"/>
+      <c r="J103" s="16"/>
+    </row>
+    <row r="104" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B104" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="G102" s="19"/>
-      <c r="H102" s="19"/>
-      <c r="I102" s="19"/>
-      <c r="J102" s="19"/>
-    </row>
-    <row r="103" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="72" t="s">
-        <v>35</v>
-      </c>
-      <c r="B103" s="109" t="s">
+      <c r="C104" s="85"/>
+      <c r="D104" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="C103" s="110"/>
-      <c r="D103" s="73" t="s">
-        <v>128</v>
-      </c>
-      <c r="E103" s="74" t="s">
-        <v>38</v>
-      </c>
-      <c r="F103" s="75" t="s">
+      <c r="E104" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="F104" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="16"/>
+    </row>
+    <row r="105" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="16"/>
+      <c r="B105" s="76"/>
+      <c r="C105" s="76"/>
+      <c r="D105" s="76"/>
+      <c r="E105" s="76"/>
+      <c r="F105" s="76"/>
+      <c r="G105" s="16"/>
+      <c r="H105" s="16"/>
+      <c r="I105" s="16"/>
+      <c r="J105" s="16"/>
+    </row>
+    <row r="106" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="16"/>
+      <c r="B106" s="76"/>
+      <c r="C106" s="76"/>
+      <c r="D106" s="76"/>
+      <c r="E106" s="76"/>
+      <c r="F106" s="76"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16"/>
+    </row>
+    <row r="107" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="G103" s="19"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="19"/>
-      <c r="J103" s="19"/>
-    </row>
-    <row r="104" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="B104" s="111" t="s">
+      <c r="B107" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="C104" s="112"/>
-      <c r="D104" s="77" t="s">
-        <v>136</v>
-      </c>
-      <c r="E104" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="F104" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="G104" s="19"/>
-      <c r="H104" s="19"/>
-      <c r="I104" s="19"/>
-      <c r="J104" s="19"/>
-    </row>
-    <row r="105" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="19"/>
-      <c r="B105" s="79"/>
-      <c r="C105" s="79"/>
-      <c r="D105" s="79"/>
-      <c r="E105" s="79"/>
-      <c r="F105" s="79"/>
-      <c r="G105" s="19"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="19"/>
-      <c r="J105" s="19"/>
-    </row>
-    <row r="106" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="19"/>
-      <c r="B106" s="79"/>
-      <c r="C106" s="79"/>
-      <c r="D106" s="79"/>
-      <c r="E106" s="79"/>
-      <c r="F106" s="79"/>
-      <c r="G106" s="19"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="19"/>
-      <c r="J106" s="19"/>
-    </row>
-    <row r="107" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="B107" s="79" t="s">
-        <v>138</v>
-      </c>
-      <c r="C107" s="79"/>
-      <c r="D107" s="79"/>
-      <c r="E107" s="79"/>
-      <c r="F107" s="79"/>
-      <c r="G107" s="19"/>
-      <c r="H107" s="19"/>
-      <c r="I107" s="19"/>
-      <c r="J107" s="19"/>
+      <c r="C107" s="76"/>
+      <c r="D107" s="76"/>
+      <c r="E107" s="76"/>
+      <c r="F107" s="76"/>
+      <c r="G107" s="16"/>
+      <c r="H107" s="16"/>
+      <c r="I107" s="16"/>
+      <c r="J107" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="G87:G90"/>
-    <mergeCell ref="H87:H90"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="E67:E68"/>
     <mergeCell ref="I87:I90"/>
     <mergeCell ref="J87:J90"/>
     <mergeCell ref="B100:C100"/>
@@ -6223,78 +6269,11 @@
     <mergeCell ref="D79:D80"/>
     <mergeCell ref="E79:E80"/>
     <mergeCell ref="F79:F80"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="G87:G90"/>
+    <mergeCell ref="H87:H90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
